--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1469,6 +1469,1051 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120358852</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579299</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7056134</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120358146</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579267</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7056077</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120358465</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579313</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7056062</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120357671</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579191</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7056059</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120357461</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579232</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7056135</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120357618</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579177</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7056061</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120357603</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579200</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7056104</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120358070</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579244</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7056088</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120358716</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>579331</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7056093</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -1471,7 +1471,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120358852</v>
+        <v>120358716</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1505,21 +1505,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579299</v>
+        <v>579331</v>
       </c>
       <c r="R9" t="n">
-        <v>7056134</v>
+        <v>7056093</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120358146</v>
+        <v>120357618</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,30 +1600,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1632,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579267</v>
+        <v>579177</v>
       </c>
       <c r="R10" t="n">
-        <v>7056077</v>
+        <v>7056061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120358465</v>
+        <v>120357671</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,38 +1717,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579313</v>
+        <v>579191</v>
       </c>
       <c r="R11" t="n">
-        <v>7056062</v>
+        <v>7056059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120357671</v>
+        <v>120358070</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>90576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,42 +1833,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579191</v>
+        <v>579244</v>
       </c>
       <c r="R12" t="n">
-        <v>7056059</v>
+        <v>7056088</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120357461</v>
+        <v>120358465</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,43 +1949,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579232</v>
+        <v>579313</v>
       </c>
       <c r="R13" t="n">
-        <v>7056135</v>
+        <v>7056062</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120357618</v>
+        <v>120358146</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,31 +2057,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2098,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579177</v>
+        <v>579267</v>
       </c>
       <c r="R14" t="n">
-        <v>7056061</v>
+        <v>7056077</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,7 +2161,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120357603</v>
+        <v>120358852</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2204,16 +2195,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579200</v>
+        <v>579299</v>
       </c>
       <c r="R15" t="n">
-        <v>7056104</v>
+        <v>7056134</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,12 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120358070</v>
+        <v>120357461</v>
       </c>
       <c r="B16" t="n">
-        <v>90576</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,34 +2294,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579244</v>
+        <v>579232</v>
       </c>
       <c r="R16" t="n">
-        <v>7056088</v>
+        <v>7056135</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,7 +2399,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120358716</v>
+        <v>120357603</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2435,14 +2435,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579331</v>
+        <v>579200</v>
       </c>
       <c r="R17" t="n">
-        <v>7056093</v>
+        <v>7056104</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120358716</v>
+        <v>120357671</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,38 +1483,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579331</v>
+        <v>579191</v>
       </c>
       <c r="R9" t="n">
-        <v>7056093</v>
+        <v>7056059</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120357618</v>
+        <v>120358852</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1629,14 +1628,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579177</v>
+        <v>579299</v>
       </c>
       <c r="R10" t="n">
-        <v>7056061</v>
+        <v>7056134</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120357671</v>
+        <v>120357618</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,42 +1716,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579191</v>
+        <v>579177</v>
       </c>
       <c r="R11" t="n">
-        <v>7056059</v>
+        <v>7056061</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120358070</v>
+        <v>120358146</v>
       </c>
       <c r="B12" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,38 +1833,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579244</v>
+        <v>579267</v>
       </c>
       <c r="R12" t="n">
-        <v>7056088</v>
+        <v>7056077</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120358465</v>
+        <v>120358716</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,21 +1953,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579313</v>
+        <v>579331</v>
       </c>
       <c r="R13" t="n">
-        <v>7056062</v>
+        <v>7056093</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2022,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120358146</v>
+        <v>120357603</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,42 +2066,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579267</v>
+        <v>579200</v>
       </c>
       <c r="R14" t="n">
-        <v>7056077</v>
+        <v>7056104</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2139,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120358852</v>
+        <v>120357461</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,39 +2187,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579299</v>
+        <v>579232</v>
       </c>
       <c r="R15" t="n">
-        <v>7056134</v>
+        <v>7056135</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120357461</v>
+        <v>120358465</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,43 +2308,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579232</v>
+        <v>579313</v>
       </c>
       <c r="R16" t="n">
-        <v>7056135</v>
+        <v>7056062</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120357603</v>
+        <v>120358070</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,21 +2420,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2439,10 +2444,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579200</v>
+        <v>579244</v>
       </c>
       <c r="R17" t="n">
-        <v>7056104</v>
+        <v>7056088</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,12 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -1587,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120358852</v>
+        <v>120357603</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1621,21 +1621,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579299</v>
+        <v>579200</v>
       </c>
       <c r="R10" t="n">
-        <v>7056134</v>
+        <v>7056104</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1672,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,7 +1704,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120357618</v>
+        <v>120358716</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1738,21 +1738,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579177</v>
+        <v>579331</v>
       </c>
       <c r="R11" t="n">
-        <v>7056061</v>
+        <v>7056093</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120358146</v>
+        <v>120358465</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,42 +1833,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579267</v>
+        <v>579313</v>
       </c>
       <c r="R12" t="n">
-        <v>7056077</v>
+        <v>7056062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,7 +1933,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120358716</v>
+        <v>120358852</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1971,16 +1967,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579331</v>
+        <v>579299</v>
       </c>
       <c r="R13" t="n">
-        <v>7056093</v>
+        <v>7056134</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,12 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,7 +2050,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120357603</v>
+        <v>120357618</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2088,16 +2084,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579200</v>
+        <v>579177</v>
       </c>
       <c r="R14" t="n">
-        <v>7056104</v>
+        <v>7056061</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,12 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2292,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120358465</v>
+        <v>120358146</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,38 +2300,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579313</v>
+        <v>579267</v>
       </c>
       <c r="R16" t="n">
-        <v>7056062</v>
+        <v>7056077</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120357671</v>
+        <v>120357603</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,42 +1483,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579191</v>
+        <v>579200</v>
       </c>
       <c r="R9" t="n">
-        <v>7056059</v>
+        <v>7056104</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120357603</v>
+        <v>120357671</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,38 +1600,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579200</v>
+        <v>579191</v>
       </c>
       <c r="R10" t="n">
-        <v>7056104</v>
+        <v>7056059</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,12 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,7 +1704,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120358716</v>
+        <v>120357618</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1738,16 +1738,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579331</v>
+        <v>579177</v>
       </c>
       <c r="R11" t="n">
-        <v>7056093</v>
+        <v>7056061</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,12 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120358465</v>
+        <v>120358852</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,34 +1837,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579313</v>
+        <v>579299</v>
       </c>
       <c r="R12" t="n">
-        <v>7056062</v>
+        <v>7056134</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120358852</v>
+        <v>120358465</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,39 +1954,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579299</v>
+        <v>579313</v>
       </c>
       <c r="R13" t="n">
-        <v>7056134</v>
+        <v>7056062</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120357618</v>
+        <v>120358146</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,31 +2062,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2095,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579177</v>
+        <v>579267</v>
       </c>
       <c r="R14" t="n">
-        <v>7056061</v>
+        <v>7056077</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120357461</v>
+        <v>120358716</v>
       </c>
       <c r="B15" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,43 +2182,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579232</v>
+        <v>579331</v>
       </c>
       <c r="R15" t="n">
-        <v>7056135</v>
+        <v>7056093</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2251,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,10 +2283,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120358146</v>
+        <v>120357461</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,30 +2295,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579267</v>
+        <v>579232</v>
       </c>
       <c r="R16" t="n">
-        <v>7056077</v>
+        <v>7056135</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -1938,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120358465</v>
+        <v>120358146</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,38 +1950,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579313</v>
+        <v>579267</v>
       </c>
       <c r="R13" t="n">
-        <v>7056062</v>
+        <v>7056077</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120358146</v>
+        <v>120358465</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,42 +2066,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579267</v>
+        <v>579313</v>
       </c>
       <c r="R14" t="n">
-        <v>7056077</v>
+        <v>7056062</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -1471,7 +1471,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120357603</v>
+        <v>120358852</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1505,16 +1505,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579200</v>
+        <v>579299</v>
       </c>
       <c r="R9" t="n">
-        <v>7056104</v>
+        <v>7056134</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120357671</v>
+        <v>120357603</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,42 +1600,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579191</v>
+        <v>579200</v>
       </c>
       <c r="R10" t="n">
-        <v>7056059</v>
+        <v>7056104</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1663,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1673,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120357618</v>
+        <v>120358146</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,31 +1717,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579177</v>
+        <v>579267</v>
       </c>
       <c r="R11" t="n">
-        <v>7056061</v>
+        <v>7056077</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,7 +1821,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120358852</v>
+        <v>120357618</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1862,14 +1862,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579299</v>
+        <v>579177</v>
       </c>
       <c r="R12" t="n">
-        <v>7056134</v>
+        <v>7056061</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120358146</v>
+        <v>120357461</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,30 +1950,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1982,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579267</v>
+        <v>579232</v>
       </c>
       <c r="R13" t="n">
-        <v>7056077</v>
+        <v>7056135</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2166,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120358716</v>
+        <v>120358070</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,34 +2187,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579331</v>
+        <v>579244</v>
       </c>
       <c r="R15" t="n">
-        <v>7056093</v>
+        <v>7056088</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,12 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,10 +2283,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120357461</v>
+        <v>120357671</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,47 +2295,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579232</v>
+        <v>579191</v>
       </c>
       <c r="R16" t="n">
-        <v>7056135</v>
+        <v>7056059</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120358070</v>
+        <v>120358716</v>
       </c>
       <c r="B17" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,34 +2415,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579244</v>
+        <v>579331</v>
       </c>
       <c r="R17" t="n">
-        <v>7056088</v>
+        <v>7056093</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2484,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -1471,7 +1471,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120358852</v>
+        <v>120357618</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1512,14 +1512,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579299</v>
+        <v>579177</v>
       </c>
       <c r="R9" t="n">
-        <v>7056134</v>
+        <v>7056061</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120358146</v>
+        <v>120358716</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,42 +1717,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579267</v>
+        <v>579331</v>
       </c>
       <c r="R11" t="n">
-        <v>7056077</v>
+        <v>7056093</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1790,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,7 +1822,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120357618</v>
+        <v>120358852</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1862,14 +1863,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579177</v>
+        <v>579299</v>
       </c>
       <c r="R12" t="n">
-        <v>7056061</v>
+        <v>7056134</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120357461</v>
+        <v>120358465</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,43 +1955,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579232</v>
+        <v>579313</v>
       </c>
       <c r="R13" t="n">
-        <v>7056135</v>
+        <v>7056062</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120358465</v>
+        <v>120357461</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,34 +2067,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579313</v>
+        <v>579232</v>
       </c>
       <c r="R14" t="n">
-        <v>7056062</v>
+        <v>7056135</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2283,7 +2284,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120357671</v>
+        <v>120358146</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2318,19 +2319,19 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Karlströmsslåtten, Karlströmsslåtten, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579191</v>
+        <v>579267</v>
       </c>
       <c r="R16" t="n">
-        <v>7056059</v>
+        <v>7056077</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120358716</v>
+        <v>120357671</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,38 +2412,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579331</v>
+        <v>579191</v>
       </c>
       <c r="R17" t="n">
-        <v>7056093</v>
+        <v>7056059</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,12 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2519,7 +2519,7 @@
         <v>121254474</v>
       </c>
       <c r="B18" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2519,7 +2519,7 @@
         <v>121254474</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2519,7 +2519,7 @@
         <v>121254474</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2519,7 +2519,7 @@
         <v>121254474</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2519,7 +2519,7 @@
         <v>121254474</v>
       </c>
       <c r="B18" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2626,6 +2626,104 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104243874</v>
+      </c>
+      <c r="B19" t="n">
+        <v>105775</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>579315</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7056098</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>104243874</v>
       </c>
       <c r="B19" t="n">
-        <v>105775</v>
+        <v>105778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>104243874</v>
       </c>
       <c r="B19" t="n">
-        <v>105778</v>
+        <v>105807</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>104243874</v>
       </c>
       <c r="B19" t="n">
-        <v>105807</v>
+        <v>105819</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>104243874</v>
       </c>
       <c r="B19" t="n">
-        <v>105819</v>
+        <v>105820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>104243874</v>
       </c>
       <c r="B19" t="n">
-        <v>105820</v>
+        <v>105825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>104243874</v>
       </c>
       <c r="B19" t="n">
-        <v>105825</v>
+        <v>105829</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>104243874</v>
       </c>
       <c r="B19" t="n">
-        <v>105829</v>
+        <v>105831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>104243874</v>
       </c>
       <c r="B19" t="n">
-        <v>105831</v>
+        <v>105841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2022 artfynd.xlsx
+++ b/artfynd/A 43131-2022 artfynd.xlsx
@@ -2631,7 +2631,7 @@
         <v>104243874</v>
       </c>
       <c r="B19" t="n">
-        <v>105841</v>
+        <v>105845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
